--- a/test_data/data.xlsx
+++ b/test_data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrppdex/projects/R/modular_specs_validator/test_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\r_projects\modular_specs_validator\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C3231E-56F3-554D-A21C-BFDFA4C8B612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4317E1F-9611-46C9-A3E7-DA448AC29D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ards_check_data" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,13 @@
     <t/>
   </si>
   <si>
-    <t>{"validation_module":"volcano_plot", "filter":"TRT == 'Treatment'", "pt_column":"PT", "trt_column":"TRT", "result_column":"Result", "resulttype_column":"ResultType", "pval_name":"PValue", "effect_name":"Effect"}</t>
-  </si>
-  <si>
-    <t>/Users/mrppdex/projects/R/modular_specs_validator/test_data/volcano_data.csv</t>
-  </si>
-  <si>
     <t>{"validation_module":"plot_effect", "filter":"reftrt == 'Placebo'", "measure":"mean", "difference_measure":"diff", "difference_lci":"lci", "difference_uci":"uci", "cmp_name":"Placebo", "ref_column":"reftrt", "trt_column":"trt", "resulttype_column":"resulttype", "result_column":"result"}</t>
+  </si>
+  <si>
+    <t>test_data/volcano_data.csv</t>
+  </si>
+  <si>
+    <t>{"validation_module":"volcano_plot", "filter":"TRT == 'Treatment'", "pt_column":"PT", "trt_column":"TRT", "reftrt_column": "PBO", "result_column":"Result", "resulttype_column":"ResultType", "pval_name":"PValue", "effect_name":"Effect"}</t>
   </si>
 </sst>
 </file>
@@ -380,9 +380,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -390,7 +390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -398,7 +398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -406,7 +406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -423,9 +423,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,15 +433,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -449,7 +449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -466,9 +466,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,15 +476,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
